--- a/data/sars/atlantic/tables/Atlantic_2003_Table1.xlsx
+++ b/data/sars/atlantic/tables/Atlantic_2003_Table1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/atlantic/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7F33B2-89D3-F34F-9CF4-2A88F3213604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD1C163-5FF6-D64E-8D6C-066D017681AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="500" windowWidth="35220" windowHeight="19600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -395,61 +395,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2324,7 +2324,7 @@
         <v>0.5</v>
       </c>
       <c r="H39" s="14">
-        <v>0.71499999999999997</v>
+        <v>0.7</v>
       </c>
       <c r="I39" s="7">
         <v>0</v>
@@ -2365,7 +2365,7 @@
         <v>0.5</v>
       </c>
       <c r="H40" s="14">
-        <v>0.71499999999999997</v>
+        <v>0.7</v>
       </c>
       <c r="I40" s="7">
         <v>0</v>
@@ -2640,7 +2640,7 @@
         <v>0.5</v>
       </c>
       <c r="H47" s="11">
-        <v>24817</v>
+        <v>248</v>
       </c>
       <c r="I47" s="12">
         <v>0</v>
